--- a/QRcode WIth Sl.Nos/QRcode WIth Sl.Nos/dist/QR_Output.xlsx
+++ b/QRcode WIth Sl.Nos/QRcode WIth Sl.Nos/dist/QR_Output.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="sdkvmvn" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="MPU" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -133,7 +133,7 @@
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="523875" cy="523875"/>
+    <ext cx="733425" cy="733425"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -158,7 +158,7 @@
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="523875" cy="523875"/>
+    <ext cx="733425" cy="733425"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -183,7 +183,7 @@
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="523875" cy="523875"/>
+    <ext cx="733425" cy="733425"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -208,7 +208,7 @@
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="523875" cy="523875"/>
+    <ext cx="733425" cy="733425"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -233,7 +233,7 @@
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="523875" cy="523875"/>
+    <ext cx="733425" cy="733425"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -258,7 +258,7 @@
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="523875" cy="523875"/>
+    <ext cx="733425" cy="733425"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -283,7 +283,7 @@
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="523875" cy="523875"/>
+    <ext cx="733425" cy="733425"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -308,7 +308,7 @@
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="523875" cy="523875"/>
+    <ext cx="733425" cy="733425"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -328,19 +328,69 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="733425" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="733425" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
       <col>0</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="523875" cy="523875"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
+    <ext cx="733425" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId11"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -358,14 +408,14 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="523875" cy="523875"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="10" name="Image 10" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId10"/>
+    <ext cx="733425" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId12"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -383,14 +433,14 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="523875" cy="523875"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="11" name="Image 11" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId11"/>
+    <ext cx="733425" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId13"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -408,14 +458,14 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="523875" cy="523875"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="12" name="Image 12" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId12"/>
+    <ext cx="733425" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId14"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -433,14 +483,14 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="523875" cy="523875"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="13" name="Image 13" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId13"/>
+    <ext cx="733425" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId15"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -458,14 +508,14 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="523875" cy="523875"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="14" name="Image 14" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId14"/>
+    <ext cx="733425" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId16"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -483,14 +533,14 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="523875" cy="523875"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="15" name="Image 15" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId15"/>
+    <ext cx="733425" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId17"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -508,14 +558,64 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="523875" cy="523875"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="16" name="Image 16" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId16"/>
+    <ext cx="733425" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId18"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="733425" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId19"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="733425" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId20"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -533,14 +633,14 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="523875" cy="523875"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="17" name="Image 17" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId17"/>
+    <ext cx="733425" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="21" name="Image 21" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId21"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -558,14 +658,14 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="523875" cy="523875"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="18" name="Image 18" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId18"/>
+    <ext cx="733425" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="22" name="Image 22" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId22"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -583,14 +683,14 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="523875" cy="523875"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="19" name="Image 19" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId19"/>
+    <ext cx="733425" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="23" name="Image 23" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId23"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -608,14 +708,14 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="523875" cy="523875"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="20" name="Image 20" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId20"/>
+    <ext cx="733425" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="24" name="Image 24" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId24"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -633,14 +733,14 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="523875" cy="523875"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="21" name="Image 21" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId21"/>
+    <ext cx="733425" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="25" name="Image 25" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId25"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -658,14 +758,14 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="523875" cy="523875"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="22" name="Image 22" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId22"/>
+    <ext cx="733425" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId26"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -683,14 +783,14 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="523875" cy="523875"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="23" name="Image 23" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId23"/>
+    <ext cx="733425" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="27" name="Image 27" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId27"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -708,14 +808,64 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="523875" cy="523875"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="24" name="Image 24" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId24"/>
+    <ext cx="733425" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId28"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="733425" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId29"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="733425" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="30" name="Image 30" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId30"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -733,14 +883,14 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="523875" cy="523875"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="25" name="Image 25" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId25"/>
+    <ext cx="733425" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="31" name="Image 31" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId31"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -758,14 +908,14 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="523875" cy="523875"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="26" name="Image 26" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId26"/>
+    <ext cx="733425" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="32" name="Image 32" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId32"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -783,14 +933,14 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="523875" cy="523875"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="27" name="Image 27" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId27"/>
+    <ext cx="733425" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="33" name="Image 33" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId33"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -808,14 +958,14 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="523875" cy="523875"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="28" name="Image 28" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId28"/>
+    <ext cx="733425" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="34" name="Image 34" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId34"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -833,14 +983,14 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="523875" cy="523875"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="29" name="Image 29" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId29"/>
+    <ext cx="733425" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="35" name="Image 35" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId35"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -858,14 +1008,14 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="523875" cy="523875"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="30" name="Image 30" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId30"/>
+    <ext cx="733425" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="36" name="Image 36" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId36"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -883,14 +1033,14 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="523875" cy="523875"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="31" name="Image 31" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId31"/>
+    <ext cx="733425" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="37" name="Image 37" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId37"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -908,14 +1058,64 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="523875" cy="523875"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="32" name="Image 32" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId32"/>
+    <ext cx="733425" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="38" name="Image 38" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId38"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="733425" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="39" name="Image 39" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId39"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="733425" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="40" name="Image 40" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId40"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -933,14 +1133,14 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="523875" cy="523875"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="33" name="Image 33" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId33"/>
+    <ext cx="733425" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="41" name="Image 41" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId41"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -958,14 +1158,14 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="523875" cy="523875"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="34" name="Image 34" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId34"/>
+    <ext cx="733425" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="42" name="Image 42" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId42"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -983,14 +1183,14 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="523875" cy="523875"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="35" name="Image 35" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId35"/>
+    <ext cx="733425" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="43" name="Image 43" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId43"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1008,14 +1208,364 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="523875" cy="523875"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="36" name="Image 36" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId36"/>
+    <ext cx="733425" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="44" name="Image 44" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId44"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="733425" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="45" name="Image 45" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId45"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="733425" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="46" name="Image 46" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId46"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="733425" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="47" name="Image 47" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId47"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="733425" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="48" name="Image 48" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId48"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="733425" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="49" name="Image 49" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId49"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="733425" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="50" name="Image 50" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId50"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="733425" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="51" name="Image 51" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId51"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="733425" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="52" name="Image 52" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId52"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="733425" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="53" name="Image 53" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId53"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="733425" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="54" name="Image 54" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId54"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="733425" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="55" name="Image 55" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId55"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="733425" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="56" name="Image 56" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId56"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="733425" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="57" name="Image 57" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId57"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="733425" cy="733425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="58" name="Image 58" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId58"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1329,13 +1879,16 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="45" customHeight="1"/>
-    <row r="2" ht="45" customHeight="1"/>
-    <row r="3" ht="45" customHeight="1"/>
-    <row r="4" ht="45" customHeight="1"/>
-    <row r="5" ht="45" customHeight="1"/>
+    <row r="1" ht="60" customHeight="1"/>
+    <row r="2" ht="60" customHeight="1"/>
+    <row r="3" ht="60" customHeight="1"/>
+    <row r="4" ht="60" customHeight="1"/>
+    <row r="5" ht="60" customHeight="1"/>
+    <row r="6" ht="60" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9"/>

--- a/QRcode WIth Sl.Nos/QRcode WIth Sl.Nos/dist/QR_Output.xlsx
+++ b/QRcode WIth Sl.Nos/QRcode WIth Sl.Nos/dist/QR_Output.xlsx
@@ -7,7 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="MPU" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Main Processing Unit (MPU)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Power Supply Unit (PSU)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SLAVE DESTINATION DISPLY UNIT(DDB)" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -133,7 +135,7 @@
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -158,7 +160,7 @@
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -183,7 +185,7 @@
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -208,7 +210,7 @@
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -233,7 +235,7 @@
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -258,7 +260,7 @@
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -283,7 +285,7 @@
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -308,7 +310,7 @@
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -333,7 +335,7 @@
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -358,7 +360,7 @@
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -383,7 +385,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -408,7 +410,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -433,7 +435,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -458,7 +460,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="14" name="Image 14" descr="Picture"/>
@@ -483,7 +485,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="15" name="Image 15" descr="Picture"/>
@@ -508,7 +510,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="16" name="Image 16" descr="Picture"/>
@@ -533,7 +535,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="17" name="Image 17" descr="Picture"/>
@@ -558,7 +560,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="18" name="Image 18" descr="Picture"/>
@@ -583,7 +585,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="19" name="Image 19" descr="Picture"/>
@@ -608,7 +610,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="20" name="Image 20" descr="Picture"/>
@@ -633,7 +635,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="21" name="Image 21" descr="Picture"/>
@@ -658,7 +660,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="22" name="Image 22" descr="Picture"/>
@@ -683,7 +685,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="23" name="Image 23" descr="Picture"/>
@@ -708,7 +710,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="24" name="Image 24" descr="Picture"/>
@@ -733,7 +735,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="25" name="Image 25" descr="Picture"/>
@@ -758,7 +760,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="26" name="Image 26" descr="Picture"/>
@@ -783,7 +785,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="27" name="Image 27" descr="Picture"/>
@@ -808,7 +810,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="28" name="Image 28" descr="Picture"/>
@@ -833,7 +835,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="29" name="Image 29" descr="Picture"/>
@@ -858,7 +860,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="30" name="Image 30" descr="Picture"/>
@@ -883,7 +885,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="31" name="Image 31" descr="Picture"/>
@@ -908,7 +910,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="32" name="Image 32" descr="Picture"/>
@@ -933,7 +935,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="33" name="Image 33" descr="Picture"/>
@@ -958,7 +960,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="34" name="Image 34" descr="Picture"/>
@@ -983,7 +985,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="35" name="Image 35" descr="Picture"/>
@@ -1008,7 +1010,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="36" name="Image 36" descr="Picture"/>
@@ -1033,7 +1035,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="37" name="Image 37" descr="Picture"/>
@@ -1058,7 +1060,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="38" name="Image 38" descr="Picture"/>
@@ -1083,7 +1085,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="39" name="Image 39" descr="Picture"/>
@@ -1108,7 +1110,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="40" name="Image 40" descr="Picture"/>
@@ -1133,7 +1135,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="41" name="Image 41" descr="Picture"/>
@@ -1158,7 +1160,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="42" name="Image 42" descr="Picture"/>
@@ -1183,7 +1185,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="43" name="Image 43" descr="Picture"/>
@@ -1208,7 +1210,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="44" name="Image 44" descr="Picture"/>
@@ -1233,7 +1235,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="45" name="Image 45" descr="Picture"/>
@@ -1258,7 +1260,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="46" name="Image 46" descr="Picture"/>
@@ -1283,7 +1285,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="47" name="Image 47" descr="Picture"/>
@@ -1301,14 +1303,2374 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
   <oneCellAnchor>
     <from>
       <col>7</col>
       <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId16"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId17"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId18"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId19"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId20"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="21" name="Image 21" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId21"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="22" name="Image 22" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId22"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="23" name="Image 23" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId23"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="24" name="Image 24" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId24"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="25" name="Image 25" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId25"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId26"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="27" name="Image 27" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId27"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId28"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId29"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="30" name="Image 30" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId30"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="31" name="Image 31" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId31"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="32" name="Image 32" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId32"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="33" name="Image 33" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId33"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="34" name="Image 34" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId34"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="35" name="Image 35" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId35"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="36" name="Image 36" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId36"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="37" name="Image 37" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId37"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="38" name="Image 38" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId38"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="39" name="Image 39" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId39"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="40" name="Image 40" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId40"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="41" name="Image 41" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId41"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="42" name="Image 42" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId42"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="43" name="Image 43" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId43"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="44" name="Image 44" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId44"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="45" name="Image 45" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId45"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="46" name="Image 46" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId46"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="47" name="Image 47" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId47"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId16"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId17"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId18"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId19"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId20"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="21" name="Image 21" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId21"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="22" name="Image 22" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId22"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="23" name="Image 23" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId23"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="24" name="Image 24" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId24"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="25" name="Image 25" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId25"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId26"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="27" name="Image 27" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId27"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId28"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId29"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="30" name="Image 30" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId30"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="31" name="Image 31" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId31"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="32" name="Image 32" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId32"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="33" name="Image 33" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId33"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="34" name="Image 34" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId34"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="35" name="Image 35" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId35"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="36" name="Image 36" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId36"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="37" name="Image 37" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId37"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="38" name="Image 38" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId38"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="39" name="Image 39" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId39"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="40" name="Image 40" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId40"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="41" name="Image 41" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId41"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="42" name="Image 42" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId42"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="43" name="Image 43" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId43"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="44" name="Image 44" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId44"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="45" name="Image 45" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId45"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="46" name="Image 46" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId46"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="47" name="Image 47" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId47"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="48" name="Image 48" descr="Picture"/>
@@ -1333,7 +3695,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="49" name="Image 49" descr="Picture"/>
@@ -1358,7 +3720,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="50" name="Image 50" descr="Picture"/>
@@ -1383,7 +3745,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="51" name="Image 51" descr="Picture"/>
@@ -1408,7 +3770,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="52" name="Image 52" descr="Picture"/>
@@ -1433,7 +3795,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="53" name="Image 53" descr="Picture"/>
@@ -1458,7 +3820,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="54" name="Image 54" descr="Picture"/>
@@ -1483,7 +3845,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="55" name="Image 55" descr="Picture"/>
@@ -1508,7 +3870,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="56" name="Image 56" descr="Picture"/>
@@ -1533,7 +3895,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="57" name="Image 57" descr="Picture"/>
@@ -1558,7 +3920,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="733425" cy="733425"/>
+    <ext cx="714375" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="58" name="Image 58" descr="Picture"/>
@@ -1566,6 +3928,906 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId58"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="59" name="Image 59" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId59"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="60" name="Image 60" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId60"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="61" name="Image 61" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId61"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="62" name="Image 62" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId62"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="63" name="Image 63" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId63"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="64" name="Image 64" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId64"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="65" name="Image 65" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId65"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="66" name="Image 66" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId66"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="67" name="Image 67" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId67"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="68" name="Image 68" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId68"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="69" name="Image 69" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId69"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="70" name="Image 70" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId70"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="71" name="Image 71" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId71"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="72" name="Image 72" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId72"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="73" name="Image 73" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId73"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="74" name="Image 74" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId74"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="75" name="Image 75" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId75"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="76" name="Image 76" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId76"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="77" name="Image 77" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId77"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="78" name="Image 78" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId78"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="79" name="Image 79" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId79"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="80" name="Image 80" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId80"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="81" name="Image 81" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId81"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="82" name="Image 82" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId82"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="83" name="Image 83" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId83"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="84" name="Image 84" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId84"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="85" name="Image 85" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId85"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="86" name="Image 86" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId86"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="87" name="Image 87" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId87"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="88" name="Image 88" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId88"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="89" name="Image 89" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId89"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="90" name="Image 90" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId90"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="91" name="Image 91" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId91"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="92" name="Image 92" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId92"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="93" name="Image 93" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId93"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="94" name="Image 94" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId94"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1888,7 +5150,77 @@
     <row r="3" ht="60" customHeight="1"/>
     <row r="4" ht="60" customHeight="1"/>
     <row r="5" ht="60" customHeight="1"/>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="60" customHeight="1"/>
+    <row r="2" ht="60" customHeight="1"/>
+    <row r="3" ht="60" customHeight="1"/>
+    <row r="4" ht="60" customHeight="1"/>
+    <row r="5" ht="60" customHeight="1"/>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="60" customHeight="1"/>
+    <row r="2" ht="60" customHeight="1"/>
+    <row r="3" ht="60" customHeight="1"/>
+    <row r="4" ht="60" customHeight="1"/>
+    <row r="5" ht="60" customHeight="1"/>
     <row r="6" ht="60" customHeight="1"/>
+    <row r="7" ht="60" customHeight="1"/>
+    <row r="8" ht="60" customHeight="1"/>
+    <row r="9" ht="60" customHeight="1"/>
+    <row r="10" ht="60" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9"/>
